--- a/Decks/Kadena.xlsx
+++ b/Decks/Kadena.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B40D44-6E57-4B2A-8DFC-91E26E59D404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DCB8E8-4E41-4780-A5E5-864266759A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
@@ -191,9 +191,6 @@
     <t>Liberator, Urza's Battlethopter</t>
   </si>
   <si>
-    <t>Oblivious Bookworm</t>
-  </si>
-  <si>
     <t>Grazilaxx, Illithid Scholar</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>Northampton Farm</t>
+  </si>
+  <si>
+    <t>Mana Sculpt</t>
   </si>
 </sst>
 </file>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -818,14 +818,14 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B61" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B60" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -867,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -912,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -927,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -957,10 +957,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -987,10 +987,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1002,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,10 +1062,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1167,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1182,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1212,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1242,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1257,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1287,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1467,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,10 +1482,10 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1527,10 +1527,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1542,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1556,11 +1556,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>59</v>
+      <c r="C52" t="s">
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1571,26 +1571,29 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C53" t="s">
-        <v>28</v>
+      <c r="C53" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="D53" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>34</v>
+      <c r="C54" t="s">
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="E54" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1601,14 +1604,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C55" t="s">
-        <v>17</v>
+      <c r="C55" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1680,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1691,14 +1691,14 @@
         <v>11</v>
       </c>
       <c r="B61" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B61:B101" si="1">C61&lt;&gt;D61</f>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1706,14 +1706,14 @@
         <v>11</v>
       </c>
       <c r="B62" s="5" t="b">
-        <f t="shared" ref="B62:B101" si="1">C62&lt;&gt;D62</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D63" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1755,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1766,14 +1766,14 @@
         <v>11</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C66&lt;&gt;D66</f>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D67" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1796,29 +1796,29 @@
         <v>11</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f>C68&lt;&gt;D68</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>91</v>
+        <f>C69&lt;&gt;D69</f>
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>106</v>
       </c>
       <c r="D69" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1829,11 +1829,11 @@
         <f>C70&lt;&gt;D70</f>
         <v>1</v>
       </c>
-      <c r="C70" t="s">
-        <v>107</v>
+      <c r="C70" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="D70" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1845,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1856,14 +1856,14 @@
         <v>18</v>
       </c>
       <c r="B72" s="5" t="b">
-        <f>C72&lt;&gt;D72</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D74" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,10 +1905,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" t="s">
-        <v>32</v>
+        <v>52</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1920,10 +1920,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>53</v>
+        <v>41</v>
+      </c>
+      <c r="D76" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D77" t="s">
-        <v>41</v>
+        <v>48</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1950,10 +1950,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="D78" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1965,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D79" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1980,10 +1980,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="D81" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2006,14 +2006,14 @@
         <v>18</v>
       </c>
       <c r="B82" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C82&lt;&gt;D82</f>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D82" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2022,43 +2022,43 @@
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D83" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B84" s="5" t="b">
         <f>C84&lt;&gt;D84</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B85" s="5" t="b">
-        <f>C85&lt;&gt;D85</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D85" t="s">
-        <v>46</v>
+        <v>91</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2067,13 +2067,13 @@
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>92</v>
+        <v>36</v>
+      </c>
+      <c r="D86" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2082,13 +2082,13 @@
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2096,29 +2096,29 @@
         <v>19</v>
       </c>
       <c r="B88" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C88&lt;&gt;D88</f>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D88" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B89" s="5" t="b">
         <f>C89&lt;&gt;D89</f>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="D89" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2130,10 +2130,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D90" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -2160,10 +2160,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D92" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I92" s="5"/>
     </row>
@@ -2176,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -2191,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
         <v>37</v>
       </c>
       <c r="E95" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -2224,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D96" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K96" s="5"/>
     </row>
@@ -2240,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I97" s="5"/>
     </row>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D98" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -2271,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H99" s="5"/>
     </row>
@@ -2302,10 +2302,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Kadena.xlsx
+++ b/Decks/Kadena.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DCB8E8-4E41-4780-A5E5-864266759A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554CECEA-FAF6-4109-B351-3A42ABCE2A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="113">
   <si>
     <t>Função</t>
   </si>
@@ -366,9 +366,6 @@
   </si>
   <si>
     <t>Ash Barrens</t>
-  </si>
-  <si>
-    <t>Curator Beastie</t>
   </si>
   <si>
     <t>Aphetto Exterminator</t>
@@ -1107,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
         <v>67</v>
@@ -1812,10 +1809,10 @@
       </c>
       <c r="B69" s="5" t="b">
         <f>C69&lt;&gt;D69</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="D69" t="s">
         <v>68</v>
@@ -1830,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D70" t="s">
         <v>61</v>
@@ -2115,10 +2112,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">

--- a/Decks/Kadena.xlsx
+++ b/Decks/Kadena.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554CECEA-FAF6-4109-B351-3A42ABCE2A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88016A8C-32F6-4659-9E9F-6F64F0B1C330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="111">
   <si>
     <t>Função</t>
   </si>
@@ -146,9 +146,6 @@
     <t>Bane of the Living</t>
   </si>
   <si>
-    <t>Trail of Mystery</t>
-  </si>
-  <si>
     <t>Yedora, Grave Gardener</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>Mystic Forge</t>
   </si>
   <si>
-    <t>Forsaken Monument</t>
-  </si>
-  <si>
     <t>Panoptic Projektor</t>
   </si>
   <si>
@@ -335,9 +329,6 @@
     <t>Twilight Mire</t>
   </si>
   <si>
-    <t>Chord of Calling</t>
-  </si>
-  <si>
     <t>Tear Asunder</t>
   </si>
   <si>
@@ -375,6 +366,9 @@
   </si>
   <si>
     <t>Mana Sculpt</t>
+  </si>
+  <si>
+    <t>Zimone, Mystery Unraveler</t>
   </si>
 </sst>
 </file>
@@ -804,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -819,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -834,10 +828,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -849,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -864,10 +858,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -879,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -894,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -909,10 +903,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -924,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -939,10 +933,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -954,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -969,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -984,10 +978,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -999,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1014,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1029,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1044,10 +1038,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1059,10 +1053,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1074,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1089,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1104,10 +1098,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,10 +1113,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1134,10 +1128,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1149,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1164,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1179,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1194,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1209,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1224,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1239,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1254,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1269,10 +1263,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,10 +1278,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1299,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1314,10 +1308,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1329,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,10 +1458,10 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1479,10 +1473,10 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1509,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1521,13 +1515,13 @@
       </c>
       <c r="B50" s="5" t="b">
         <f>C50&lt;&gt;D50</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1539,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1590,7 +1584,7 @@
         <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1677,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1722,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1737,10 +1731,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1782,10 +1776,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1797,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D68" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,10 +1806,10 @@
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,10 +1821,10 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1857,10 +1851,10 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1902,10 +1896,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1917,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1962,10 +1956,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D79" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1992,10 +1986,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D81" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2007,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D82" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2022,10 +2016,10 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2037,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D84" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2052,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2064,13 +2058,13 @@
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="D86" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2082,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2097,10 +2091,10 @@
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2112,10 +2106,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D89" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2127,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D90" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2142,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -2157,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D92" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I92" s="5"/>
     </row>
@@ -2173,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -2188,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -2203,13 +2197,13 @@
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E95" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -2221,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D96" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K96" s="5"/>
     </row>
@@ -2237,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I97" s="5"/>
     </row>
@@ -2253,10 +2247,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D98" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -2268,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H99" s="5"/>
     </row>
@@ -2284,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -2299,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Kadena.xlsx
+++ b/Decks/Kadena.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88016A8C-32F6-4659-9E9F-6F64F0B1C330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EE3A01-500C-4811-B4EB-25051891B53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="110">
   <si>
     <t>Função</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Voidmage Apprentice</t>
   </si>
   <si>
-    <t>Vannifar, Evolved Enigma</t>
-  </si>
-  <si>
     <t>Mischievous Quanar</t>
   </si>
   <si>
@@ -347,9 +344,6 @@
     <t>Overgrown Zealot</t>
   </si>
   <si>
-    <t>Brine Elemental</t>
-  </si>
-  <si>
     <t>Familiar's Ruse</t>
   </si>
   <si>
@@ -369,6 +363,9 @@
   </si>
   <si>
     <t>Zimone, Mystery Unraveler</t>
+  </si>
+  <si>
+    <t>Lightning Greaves</t>
   </si>
 </sst>
 </file>
@@ -798,10 +795,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -813,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -828,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -843,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -858,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -873,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -888,7 +885,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -903,10 +900,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -918,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -933,10 +930,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -948,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -963,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -978,10 +975,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -993,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1008,10 +1005,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1023,10 +1020,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1038,10 +1035,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1053,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1068,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1083,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1098,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1113,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1128,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1143,10 +1140,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1158,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1173,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1188,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1203,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1218,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1233,10 +1230,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,10 +1245,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1293,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1308,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1383,10 +1380,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1413,10 +1410,10 @@
         <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1428,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1458,10 +1455,10 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1473,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1503,10 +1500,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1518,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1533,10 +1530,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1584,7 +1581,7 @@
         <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1671,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1731,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1791,10 +1788,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1806,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,13 +1815,13 @@
       </c>
       <c r="B70" s="5" t="b">
         <f>C70&lt;&gt;D70</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,10 +1848,10 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,10 +1893,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1911,10 +1908,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1926,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1941,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1986,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D81" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2001,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D82" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2016,10 +2013,10 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2031,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2046,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2061,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D86" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2072,29 +2069,29 @@
         <v>19</v>
       </c>
       <c r="B87" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C87&lt;&gt;D87</f>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B88" s="5" t="b">
         <f>C88&lt;&gt;D88</f>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="D88" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2106,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D89" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2117,14 +2114,14 @@
         <v>20</v>
       </c>
       <c r="B90" s="5" t="b">
-        <f>C90&lt;&gt;D90</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2136,11 +2133,12 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="I91" s="5"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -2151,12 +2149,11 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D92" t="s">
-        <v>97</v>
-      </c>
-      <c r="I92" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
@@ -2167,25 +2164,28 @@
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C94&lt;&gt;D94</f>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>104</v>
+        <v>36</v>
+      </c>
+      <c r="E94" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -2197,13 +2197,10 @@
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E95" t="s">
-        <v>67</v>
+        <v>109</v>
+      </c>
+      <c r="D95" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -2215,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D96" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K96" s="5"/>
     </row>
@@ -2231,10 +2228,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I97" s="5"/>
     </row>
@@ -2247,10 +2244,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -2262,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H99" s="5"/>
     </row>
@@ -2278,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -2293,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
